--- a/Ciclo 02 - 2026/grupos inscripcion.xlsx
+++ b/Ciclo 02 - 2026/grupos inscripcion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663A945F-4228-4E07-8D16-5C403074535D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8592601E-80F2-4B67-A2BF-0ACB13B26E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{E3196F86-ED1D-4AB3-8587-FA6138E8974A}"/>
   </bookViews>
@@ -88,25 +88,25 @@
     <t>ANF115</t>
   </si>
   <si>
-    <t>Ingra  Ligia Marcela Lazo</t>
-  </si>
-  <si>
-    <t>Ronald Fransisco Hernandez</t>
-  </si>
-  <si>
-    <t>Ingra Karen Elvira Peñate</t>
-  </si>
-  <si>
-    <t>Ing Nelson Stanley Belloso</t>
-  </si>
-  <si>
-    <t>Ing Gabriel Alejandro Dominguez</t>
-  </si>
-  <si>
     <t>CET</t>
   </si>
   <si>
     <t>CET115</t>
+  </si>
+  <si>
+    <t>Ing.</t>
+  </si>
+  <si>
+    <t>Ing.  Ligia Marcela Lazo</t>
+  </si>
+  <si>
+    <t>Ing. Karen Elvira Peñate</t>
+  </si>
+  <si>
+    <t>Ing. Nelson Stanley Belloso</t>
+  </si>
+  <si>
+    <t>Ing. Gabriel Alejandro Dominguez</t>
   </si>
 </sst>
 </file>
@@ -890,7 +890,7 @@
       <c r="G2" s="12"/>
       <c r="H2" s="29"/>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -919,7 +919,7 @@
       <c r="G4" s="14"/>
       <c r="H4" s="29"/>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -952,7 +952,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -997,7 +997,7 @@
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="41"/>
       <c r="B10" s="45" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
@@ -1010,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1054,7 +1054,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
